--- a/artfynd/A 62534-2022 artfynd.xlsx
+++ b/artfynd/A 62534-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62534-2022 artfynd.xlsx
+++ b/artfynd/A 62534-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY110"/>
+  <dimension ref="A1:AZ110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972798</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972782</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972799</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206421</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1170,6 +1195,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206423</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1271,6 +1301,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206424</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1368,6 +1403,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106208518</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1465,6 +1505,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106208519</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1562,6 +1607,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106208520</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1659,6 +1709,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972788</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1756,6 +1811,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972796</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1862,6 +1922,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206405</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1959,6 +2024,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972786</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2060,6 +2130,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206411</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2161,6 +2236,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206412</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2258,6 +2338,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106208512</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2355,6 +2440,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106208515</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2452,6 +2542,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106208516</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2549,6 +2644,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972791</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2650,6 +2750,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206406</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2747,6 +2852,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972785</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2844,6 +2954,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106208513</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2941,6 +3056,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972792</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3038,6 +3158,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972800</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3140,6 +3265,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972797</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3237,6 +3367,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972787</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3353,6 +3488,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106236220</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3451,6 +3591,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972789</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3549,6 +3694,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972790</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3646,6 +3796,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972795</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3743,6 +3898,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972783</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3840,6 +4000,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972784</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3937,6 +4102,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972823</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4034,6 +4204,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110171109</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4141,6 +4316,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105936111</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4247,6 +4427,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206551</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4348,6 +4533,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206415</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4449,6 +4639,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206416</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4565,6 +4760,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206417</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4662,6 +4862,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206548</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4764,6 +4969,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972824</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4866,6 +5076,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972825</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4968,6 +5183,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972827</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5070,6 +5290,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972828</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5168,6 +5393,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105934583</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5269,6 +5499,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206488</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5366,6 +5601,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109966921</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5463,6 +5703,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972822</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5560,6 +5805,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109966860</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5657,6 +5907,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109966861</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5773,6 +6028,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206550</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5870,6 +6130,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109966898</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5968,6 +6233,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972814</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6066,6 +6336,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972815</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6164,6 +6439,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972816</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6261,6 +6541,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109966820</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6358,6 +6643,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109966821</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6455,6 +6745,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109966822</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6552,6 +6847,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972801</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6650,6 +6950,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105935845</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6751,6 +7056,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206407</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6852,6 +7162,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206409</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6953,6 +7268,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206413</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7050,6 +7370,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206547</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7156,6 +7481,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106208501</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7253,6 +7583,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106208502</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7350,6 +7685,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106208503</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7451,6 +7791,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106208504</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7548,6 +7893,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106208505</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7645,6 +7995,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106208506</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7742,6 +8097,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106208507</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7839,6 +8199,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106208514</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7940,6 +8305,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106208517</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8037,6 +8407,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972811</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8135,6 +8510,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105934447</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8233,6 +8613,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105936121</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8334,6 +8719,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206410</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8432,6 +8822,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105929847</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8533,6 +8928,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206408</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8634,6 +9034,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206414</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8731,6 +9136,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106206549</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8828,6 +9238,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972812</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8948,6 +9363,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106208508</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9050,6 +9470,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972803</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9152,6 +9577,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972805</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9254,6 +9684,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972806</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9359,6 +9794,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106208500</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9461,6 +9901,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109966830</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9563,6 +10008,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109966832</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9660,6 +10110,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972807</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9757,6 +10212,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972813</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9859,6 +10319,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109966908</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9961,6 +10426,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109966909</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10063,6 +10533,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109966910</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10165,6 +10640,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109966912</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10267,6 +10747,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109966914</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10369,6 +10854,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109966916</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10471,6 +10961,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972817</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10573,6 +11068,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972818</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10675,6 +11175,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972819</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10777,6 +11282,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972820</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10874,6 +11384,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109966855</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10971,6 +11486,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972808</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11068,6 +11588,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972809</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11165,6 +11690,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109966865</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11262,6 +11792,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109966866</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11359,6 +11894,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972810</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11456,6 +11996,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109966826</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11553,8 +12098,124 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109972802</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>